--- a/samples/spreadsheets/Bug统计表.xlsx
+++ b/samples/spreadsheets/Bug统计表.xlsx
@@ -449,7 +449,7 @@
         <v>✅ 已修复</v>
       </c>
       <c r="E2" t="str">
-        <v>王五</v>
+        <v>赵丽</v>
       </c>
       <c r="F2" t="str">
         <v>2026-06-10</v>
@@ -475,7 +475,7 @@
         <v>✅ 已修复</v>
       </c>
       <c r="E3" t="str">
-        <v>李四</v>
+        <v>刘伟</v>
       </c>
       <c r="F3" t="str">
         <v>2026-06-11</v>
@@ -501,7 +501,7 @@
         <v>✅ 已修复</v>
       </c>
       <c r="E4" t="str">
-        <v>李四</v>
+        <v>刘伟</v>
       </c>
       <c r="F4" t="str">
         <v>2026-06-12</v>
@@ -527,7 +527,7 @@
         <v>✅ 已修复</v>
       </c>
       <c r="E5" t="str">
-        <v>李四</v>
+        <v>刘伟</v>
       </c>
       <c r="F5" t="str">
         <v>2026-06-18</v>
@@ -553,7 +553,7 @@
         <v>🔄 修复中</v>
       </c>
       <c r="E6" t="str">
-        <v>李四</v>
+        <v>刘伟</v>
       </c>
       <c r="F6" t="str">
         <v>2026-06-19</v>
@@ -579,7 +579,7 @@
         <v>⏳ 待修复</v>
       </c>
       <c r="E7" t="str">
-        <v>王五</v>
+        <v>赵丽</v>
       </c>
       <c r="F7" t="str">
         <v>2026-06-19</v>
@@ -605,7 +605,7 @@
         <v>⏳ 待修复</v>
       </c>
       <c r="E8" t="str">
-        <v>张三</v>
+        <v>陈强</v>
       </c>
       <c r="F8" t="str">
         <v>2026-06-20</v>
@@ -631,7 +631,7 @@
         <v>⏳ 待修复</v>
       </c>
       <c r="E9" t="str">
-        <v>王五</v>
+        <v>赵丽</v>
       </c>
       <c r="F9" t="str">
         <v>2026-06-20</v>
